--- a/5/search/FY5_Missile3_results/solutions_direction_144.0.xlsx
+++ b/5/search/FY5_Missile3_results/solutions_direction_144.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,69 +487,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117</v>
+        <v>112.5</v>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>12186.44902446673</v>
+        <v>12375.46063838017</v>
       </c>
       <c r="F2" t="n">
-        <v>-403.3163086544448</v>
+        <v>-492.22860294158</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>12186.44902446673</v>
+        <v>12336.42692827893</v>
       </c>
       <c r="I2" t="n">
-        <v>-403.3163086544448</v>
+        <v>-397.9928906254287</v>
       </c>
       <c r="J2" t="n">
-        <v>1300</v>
+        <v>1295.1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117</v>
+        <v>112.5</v>
       </c>
       <c r="B3" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>12237.29596043756</v>
+        <v>12338.72302887312</v>
       </c>
       <c r="F3" t="n">
-        <v>-503.109039363542</v>
+        <v>-403.5361678204965</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>12173.73729047402</v>
+        <v>12338.72302887312</v>
       </c>
       <c r="I3" t="n">
-        <v>-378.3681259771705</v>
+        <v>-403.5361678204965</v>
       </c>
       <c r="J3" t="n">
-        <v>1295.1</v>
+        <v>1300</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -557,37 +557,492 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12273.61520041673</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-574.3895612986114</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12182.81710046882</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-396.1882564609379</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12230.03211244173</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-488.8529349765281</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12181.90911946934</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-394.4062434125611</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B6" t="n">
+        <v>112</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12186.44902446673</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-403.3163086544448</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12186.44902446673</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-403.3163086544448</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117</v>
+      </c>
+      <c r="B7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12291.77482040631</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-610.0298222661461</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12173.73729047402</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-378.3681259771704</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B8" t="n">
+        <v>138</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12248.19173243131</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-524.4931959440628</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12185.54104346725</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-401.534295606068</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117</v>
+      </c>
+      <c r="B9" t="n">
+        <v>140</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12237.29596043756</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-503.109039363542</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12173.73729047402</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-378.3681259771705</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12130.56238831266</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-581.2067665147904</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12021.88268685174</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-403.8576123291392</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>134</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12159.82230793675</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-628.9546157186196</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12019.79269259288</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-400.4470516717229</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>136</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12147.28234238357</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-608.4912517741213</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12005.16273278083</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-376.5731270698083</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>126</v>
       </c>
-      <c r="B4" t="n">
-        <v>134.4</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B13" t="n">
+        <v>134</v>
+      </c>
+      <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>12052.0199451027</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-695.217391472085</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11815.02493137838</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-369.0217393401062</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="E13" t="n">
+        <v>12054.8413143137</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-699.1006730450845</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11818.55164289213</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-373.8758413063556</v>
+      </c>
+      <c r="J13" t="n">
         <v>1255.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11898.53611003201</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-710.3514823423473</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11623.17013754001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-387.9393529279341</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1221.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>134</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11955.68753828506</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-777.26720731515</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11607.58338438009</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-369.6896097535334</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1221.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>120</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11540.02054604794</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-753.0597472060472</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11083.77696668792</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-363.3909182079369</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1177.5</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>144</v>
+      </c>
+      <c r="B17" t="n">
+        <v>128</v>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11343.13319552011</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-796.2158033050148</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10721.80814384015</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-344.7967295443954</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1123.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
